--- a/src/components/animations/master-gtmstack-pro-library.xlsx
+++ b/src/components/animations/master-gtmstack-pro-library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Prod\GTM Stack\GTM Stack\GTM Stack\GTM-StackPro\src\components\animations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D245E17-D6D8-4867-965D-400A59A5A327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70219905-AC0A-40D1-BE3D-634DE1233EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{51F7ECEB-0731-408E-A58D-3E55042CBEB4}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="129">
   <si>
     <t>Route</t>
   </si>
@@ -136,90 +135,24 @@
     <t>DemandGenFlow.tsx</t>
   </si>
   <si>
-    <t>/expertise/</t>
-  </si>
-  <si>
     <t>Strategy &amp; Insights</t>
   </si>
   <si>
-    <t>account-based-marketing-abm</t>
-  </si>
-  <si>
     <t>Core Pages</t>
   </si>
   <si>
-    <t>about-me</t>
-  </si>
-  <si>
     <t>Systems &amp; Operations</t>
   </si>
   <si>
-    <t>ai-in-marketing</t>
-  </si>
-  <si>
     <t>Expertise - Main</t>
   </si>
   <si>
-    <t>content-engagement</t>
-  </si>
-  <si>
     <t>Content &amp; Engagement</t>
   </si>
   <si>
-    <t>content-marketing</t>
-  </si>
-  <si>
-    <t>customer-experience-cx</t>
-  </si>
-  <si>
     <t>Demand &amp; Growth</t>
   </si>
   <si>
-    <t>event-marketing</t>
-  </si>
-  <si>
-    <t>growth-marketing</t>
-  </si>
-  <si>
-    <t>lifecycle-marketing</t>
-  </si>
-  <si>
-    <t>market-research</t>
-  </si>
-  <si>
-    <t>marketing-automation</t>
-  </si>
-  <si>
-    <t>marketing-operations</t>
-  </si>
-  <si>
-    <t>martech-optimization</t>
-  </si>
-  <si>
-    <t>omnichannel-marketing</t>
-  </si>
-  <si>
-    <t>paid-advertising</t>
-  </si>
-  <si>
-    <t>sales-enablement</t>
-  </si>
-  <si>
-    <t>search-engine-optimization</t>
-  </si>
-  <si>
-    <t>social-media-marketing</t>
-  </si>
-  <si>
-    <t>strategy-&amp;-insights</t>
-  </si>
-  <si>
-    <t>systems-&amp;-operations</t>
-  </si>
-  <si>
-    <t>video-marketing</t>
-  </si>
-  <si>
     <t>/expertise/about-me</t>
   </si>
   <si>
@@ -287,13 +220,214 @@
   </si>
   <si>
     <t>IndustrialDashboard</t>
+  </si>
+  <si>
+    <t>Omni-Analytics.tsx</t>
+  </si>
+  <si>
+    <t>Developer-Marketing.tsx</t>
+  </si>
+  <si>
+    <t>ContentStrategistDashboard.tsx</t>
+  </si>
+  <si>
+    <t>Live-Email-Automation.tsx</t>
+  </si>
+  <si>
+    <t>GitHub</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Fleet-ROI-Calculator/settings</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/EdTech-Compact-ROI-Funnel-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Nexus-Industrial-Manufacturing-Tile-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/MarketingFlow-AI-Workflow-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Content-Engagement-Marketing-Dashboard-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Vidiomark-AI-Distribution-Hub</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Agency-Performance-Console-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Executive-Logistics-Dashboard-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Fleet-ROI-Calculator</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Engineering-Excellence-Workflow-Tile-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Live-Email-Automation-Ecosystem-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/GTMStack_pro</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Manufacturing-Agency-Dashboard-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/DevConsole---Content-Workflow-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Strategist-OS-Dashboard-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Industrial-ROI-Dashboard-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Experience-Dashboard</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Marketing-Analytics-Carousel</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Lifecycle-Engine-Dashboard-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Pipeline-Command-Center-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/ABM-Network-Dashboard-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Marketing-Automation-Live-Feed-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Quantum-Data-Field-Analytics-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Marketing-Analytics-Dashboard</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Marketing-360-Flight-Planner</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Analytics-Pro-Dashboard-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/GrowthFlow-SEO-Engine</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Video-Marketing-Analytics-Dashboard-</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/ABM-Pipeline-Strategy-Dashboard</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/Workflow-Visualization</t>
+  </si>
+  <si>
+    <t>https://github.com/finlin67/SEO-JSON</t>
+  </si>
+  <si>
+    <t>EdTech-Compact-ROI-Funnel-</t>
+  </si>
+  <si>
+    <t>Nexus-Industrial-Manufacturing-Tile-</t>
+  </si>
+  <si>
+    <t>MarketingFlow-AI-Workflow-</t>
+  </si>
+  <si>
+    <t>Content-Engagement-Marketing-Dashboard-</t>
+  </si>
+  <si>
+    <t>Vidiomark-AI-Distribution-Hub</t>
+  </si>
+  <si>
+    <t>Agency-Performance-Console-</t>
+  </si>
+  <si>
+    <t>Executive-Logistics-Dashboard-</t>
+  </si>
+  <si>
+    <t>Fleet-ROI-Calculator</t>
+  </si>
+  <si>
+    <t>Engineering-Excellence-Workflow-Tile-</t>
+  </si>
+  <si>
+    <t>Live-Email-Automation-Ecosystem-</t>
+  </si>
+  <si>
+    <t>GTMStack_pro</t>
+  </si>
+  <si>
+    <t>Manufacturing-Agency-Dashboard-</t>
+  </si>
+  <si>
+    <t>DevConsole---Content-Workflow-</t>
+  </si>
+  <si>
+    <t>Strategist-OS-Dashboard-</t>
+  </si>
+  <si>
+    <t>Industrial-ROI-Dashboard-</t>
+  </si>
+  <si>
+    <t>Experience-Dashboard</t>
+  </si>
+  <si>
+    <t>Marketing-Analytics-Carousel</t>
+  </si>
+  <si>
+    <t>Lifecycle-Engine-Dashboard-</t>
+  </si>
+  <si>
+    <t>Pipeline-Command-Center-</t>
+  </si>
+  <si>
+    <t>ABM-Network-Dashboard-</t>
+  </si>
+  <si>
+    <t>Marketing-Automation-Live-Feed-</t>
+  </si>
+  <si>
+    <t>Quantum-Data-Field-Analytics-</t>
+  </si>
+  <si>
+    <t>Marketing-Analytics-Dashboard</t>
+  </si>
+  <si>
+    <t>Marketing-360-Flight-Planner</t>
+  </si>
+  <si>
+    <t>Analytics-Pro-Dashboard-</t>
+  </si>
+  <si>
+    <t>GrowthFlow-SEO-Engine</t>
+  </si>
+  <si>
+    <t>Video-Marketing-Analytics-Dashboard-</t>
+  </si>
+  <si>
+    <t>ABM-Pipeline-Strategy-Dashboard</t>
+  </si>
+  <si>
+    <t>Workflow-Visualization</t>
+  </si>
+  <si>
+    <t>SEO-JSON</t>
+  </si>
+  <si>
+    <t>Git</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -429,19 +563,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -619,6 +747,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -797,10 +931,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1176,159 +1312,181 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D724E4F2-9832-4467-ADA2-DCE6A3BF5C32}">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="38.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.73046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.86328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="50.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="F1" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
+        <v>42</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="F3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
+        <v>103</v>
+      </c>
+      <c r="I5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M6" t="str">
-        <f>J6&amp;L6</f>
-        <v>/expertise/account-based-marketing-abm</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M7" t="str">
-        <f t="shared" ref="M7:M30" si="0">J7&amp;L7</f>
-        <v>/expertise/about-me</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" t="s">
-        <v>25</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -1337,440 +1495,520 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H8" t="s">
+        <v>110</v>
+      </c>
+      <c r="I8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
         <v>26</v>
       </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M8" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/ai-in-marketing</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" t="s">
+      <c r="E11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A12" t="s">
         <v>27</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B12" t="s">
         <v>28</v>
       </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
         <v>29</v>
       </c>
-      <c r="E9" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L9" s="1" t="s">
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" t="s">
+        <v>113</v>
+      </c>
+      <c r="I12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B16" s="3"/>
+      <c r="H16" t="s">
+        <v>112</v>
+      </c>
+      <c r="I16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B17" s="3"/>
+      <c r="H17" t="s">
+        <v>115</v>
+      </c>
+      <c r="I17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B18" s="3"/>
+      <c r="H18" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B19" s="3"/>
+      <c r="F19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H19" t="s">
+        <v>109</v>
+      </c>
+      <c r="I19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B20" s="3"/>
+      <c r="H20" t="s">
+        <v>121</v>
+      </c>
+      <c r="I20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B21" s="3"/>
+      <c r="H21" t="s">
+        <v>114</v>
+      </c>
+      <c r="I21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B22" s="3"/>
+      <c r="H22" t="s">
+        <v>120</v>
+      </c>
+      <c r="I22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B23" s="3"/>
+      <c r="H23" t="s">
+        <v>118</v>
+      </c>
+      <c r="I23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B24" s="3"/>
+      <c r="H24" t="s">
+        <v>100</v>
+      </c>
+      <c r="I24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B25" s="3"/>
+      <c r="H25" t="s">
+        <v>99</v>
+      </c>
+      <c r="I25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B26" s="3"/>
+      <c r="H26" t="s">
+        <v>116</v>
+      </c>
+      <c r="I26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B27" s="3"/>
+      <c r="H27" t="s">
+        <v>119</v>
+      </c>
+      <c r="I27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B28" s="3"/>
+      <c r="H28" t="s">
+        <v>127</v>
+      </c>
+      <c r="I28" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H29" t="s">
+        <v>111</v>
+      </c>
+      <c r="I29" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H30" t="s">
+        <v>124</v>
+      </c>
+      <c r="I30" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H31" t="s">
+        <v>102</v>
+      </c>
+      <c r="I31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A32" t="s">
         <v>41</v>
       </c>
-      <c r="M9" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/content-engagement</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M10" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/content-marketing</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="J11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M11" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/customer-experience-cx</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M14" t="str">
-        <f>J14&amp;L14</f>
-        <v>/expertise/paid-advertising</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A15" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M15" t="str">
-        <f>J15&amp;L15</f>
-        <v>/expertise/marketing-automation</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="J16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M16" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/event-marketing</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M17" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/growth-marketing</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A18" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M18" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/lifecycle-marketing</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="M19" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/market-research</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="21" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A21" t="s">
-        <v>64</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="M21" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/marketing-operations</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A22" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="M22" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/martech-optimization</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M23" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/omnichannel-marketing</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="25" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A25" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M25" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/sales-enablement</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A26" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M26" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/search-engine-optimization</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A27" t="s">
-        <v>70</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="M27" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/social-media-marketing</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A28" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="M28" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/strategy-&amp;-insights</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A29" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="M29" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/systems-&amp;-operations</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A30" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M30" t="str">
-        <f t="shared" si="0"/>
-        <v>/expertise/video-marketing</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A32" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>38</v>
+      <c r="H32" t="s">
+        <v>126</v>
+      </c>
+      <c r="I32" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A33" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="B33" s="3"/>
     </row>
     <row r="34" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
-        <v>76</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A37" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="B37" s="3"/>
     </row>
     <row r="38" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
-        <v>77</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+        <v>43</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
-        <v>80</v>
+        <v>44</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B40" s="3"/>
+    </row>
+    <row r="41" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A45" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A46" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A48" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A49" t="s">
+        <v>27</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A50" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A51" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H3:I32">
+    <sortCondition ref="H2:H32"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1778,7 +2016,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94CBA77-BFFA-4ACF-B3E3-7C8A97D3C527}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
@@ -1788,7 +2026,7 @@
     <col min="5" max="5" width="8.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1804,8 +2042,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1822,7 +2063,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1839,7 +2080,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1856,7 +2097,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1873,7 +2114,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1890,7 +2131,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -1907,7 +2148,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1924,7 +2165,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1941,9 +2182,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -1958,24 +2199,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C12" t="s">
         <v>7</v>
       </c>
@@ -1983,15 +2224,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C13" t="s">
         <v>7</v>
       </c>
       <c r="E13" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C14" t="s">
         <v>7</v>
       </c>
@@ -1999,7 +2243,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C15" t="s">
         <v>7</v>
       </c>
@@ -2007,7 +2251,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C16" t="s">
         <v>7</v>
       </c>
